--- a/data/demo/Юго-восток заявки.xlsx
+++ b/data/demo/Юго-восток заявки.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Домодедово, проезд.Советский 1-й, д. 1А</t>
+          <t>Домодедово, проезд.Советский 1-й, д. 1А, кв. 44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Гурьевский, д. 23 к 1</t>
+          <t>Город Москва, проезд.Гурьевский, д. 23 к 1, кв. 251</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Кустанайская, д. 8 к 1</t>
+          <t>Город Москва, ул.Кустанайская, д. 8 к 1, кв. 87</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Город Москва, ш.Каширское, д. 136</t>
+          <t>Город Москва, ш.Каширское, д. 136, кв. 172</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Зеленая, д. 85</t>
+          <t>Домодедово, ул.Зеленая, д. 85, кв. 18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Москворечье, д. 4 к 6</t>
+          <t>Город Москва, ул.Москворечье, д. 4 к 6, кв. 22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Загорьевский, д. 9</t>
+          <t>Город Москва, проезд.Загорьевский, д. 9, кв. 72</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Город Москва, ул.6-я Радиальная, д. 5 к 3</t>
+          <t>Город Москва, ул.6-я Радиальная, д. 5 к 3, кв. 1020</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Бирюлёвская, д. 39</t>
+          <t>Город Москва, ул.Бирюлёвская, д. 39, кв. 86</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Кашира, ул.Победы, д. 9</t>
+          <t>Кашира, ул.Победы, д. 9, кв. 36</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Братеевская, д. 18 к 1</t>
+          <t>Город Москва, ул.Братеевская, д. 18 к 1, кв. 10</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Ореховый, д. 35 к 1</t>
+          <t>Город Москва, б-р.Ореховый, д. 35 к 1, кв. 74</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Ореховый, д. 35 к 1</t>
+          <t>Город Москва, б-р.Ореховый, д. 35 к 1, кв. 74</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Пролетарский, д. 14А</t>
+          <t>Город Москва, пр-кт.Пролетарский, д. 14А, кв. 67</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Корнеева, д. 50</t>
+          <t>Домодедово, ул.Корнеева, д. 50, кв. 65</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Корнеева, д. 40</t>
+          <t>Домодедово, ул.Корнеева, д. 40, кв. 186</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Зеленая, д. 85</t>
+          <t>Домодедово, ул.Зеленая, д. 85, кв. 18</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Ереванская, д. 29</t>
+          <t>Город Москва, ул.Ереванская, д. 29, кв. 29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Севанская, д. 15 к 1</t>
+          <t>Город Москва, ул.Севанская, д. 15 к 1, кв. 74</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Город Москва, ул.6-я Радиальная, д. 7/1 к 2</t>
+          <t>Город Москва, ул.6-я Радиальная, д. 7/1 к 2, кв. 586</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Загорьевский, д. 9</t>
+          <t>Город Москва, проезд.Загорьевский, д. 9, кв. 72</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Кашира, ул.Садовая, д. 18</t>
+          <t>Кашира, ул.Садовая, д. 18, кв. 77</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Кашира, ул.Садовая, д. 2/11</t>
+          <t>Кашира, ул.Садовая, д. 2/11, кв. 30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Паромная, д. 9 к 1</t>
+          <t>Город Москва, ул.Паромная, д. 9 к 1, кв. 36</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Братеевская, д. 16 к 1</t>
+          <t>Город Москва, ул.Братеевская, д. 16 к 1, кв. 208</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Борисовские Пруды, д. 20 к 1</t>
+          <t>Город Москва, ул.Борисовские Пруды, д. 20 к 1, кв. 429</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Кашира, ул.Юбилейная, д. 9</t>
+          <t>Кашира, ул.Юбилейная, д. 9, кв. 29</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Кашира, ул.8 Марта, д. 22</t>
+          <t>Кашира, ул.8 Марта, д. 22, кв. 52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Ореховый, д. 7 к 1</t>
+          <t>Город Москва, б-р.Ореховый, д. 7 к 1, кв. 71</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Город Москва, ш.Каширское, д. 94 к 1</t>
+          <t>Город Москва, ш.Каширское, д. 94 к 1, кв. 71</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Ореховый, д. 11 к 1</t>
+          <t>Город Москва, б-р.Ореховый, д. 11 к 1, кв. 314</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Борисовский, д. 44 к 3</t>
+          <t>Город Москва, проезд.Борисовский, д. 44 к 3, кв. 515</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Ореховый, д. 41</t>
+          <t>Город Москва, проезд.Ореховый, д. 41, кв. 24</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Ильюшина, д. 20</t>
+          <t>Домодедово, ул.Ильюшина, д. 20, кв. 270</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Кашира, ул.Юбилейная, д. 8</t>
+          <t>Кашира, ул.Юбилейная, д. 8, кв. 34</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Кустанайская, д. 9 к 1</t>
+          <t>Город Москва, ул.Кустанайская, д. 9 к 1, кв. 352</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Пролетарский, д. 18 к 4</t>
+          <t>Город Москва, пр-кт.Пролетарский, д. 18 к 4, кв. 85</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Борисовские Пруды, д. 20 к 1</t>
+          <t>Город Москва, ул.Борисовские Пруды, д. 20 к 1, кв. 22</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Кашира, ул.Кржижановского, д. 7</t>
+          <t>Кашира, ул.Кржижановского, д. 7, кв. 45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Медынская, д. 5 к 1</t>
+          <t>Город Москва, ул.Медынская, д. 5 к 1, кв. 128</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Гагарина, д. 55/2</t>
+          <t>Домодедово, ул.Гагарина, д. 55/2, кв. 7</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Домодедово, ул.1-я Коммунистическая, д. 39</t>
+          <t>Домодедово, ул.1-я Коммунистическая, д. 39, кв. 44</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Борисовские Пруды, д. 48 к 2</t>
+          <t>Город Москва, ул.Борисовские Пруды, д. 48 к 2, кв. 319</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ступино, ул.Калинина, д. 34</t>
+          <t>Ступино, ул.Калинина, д. 34, кв. 18</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Шипиловский, д. 59 к 2</t>
+          <t>Город Москва, проезд.Шипиловский, д. 59 к 2, кв. 255</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Востряковский, д. 15 к 2</t>
+          <t>Город Москва, проезд.Востряковский, д. 15 к 2, кв. 199</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Бирюлёвская, д. 58 к 3</t>
+          <t>Город Москва, ул.Бирюлёвская, д. 58 к 3, кв. 1094</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Домодедовская, д. 31</t>
+          <t>Город Москва, ул.Домодедовская, д. 31, кв. 150</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Весёлая, д. 33 к 7</t>
+          <t>Город Москва, ул.Весёлая, д. 33 к 7, кв. 63</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ступино, ул.Калинина, д. 34</t>
+          <t>Ступино, ул.Калинина, д. 34, кв. 18</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Ильюшина, д. 11 к 2</t>
+          <t>Домодедово, ул.Ильюшина, д. 11 к 2, кв. 6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Востряковский, д. 15 к 4</t>
+          <t>Город Москва, проезд.Востряковский, д. 15 к 4, кв. 73</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Домодедово, ул.Корнеева, д. 48</t>
+          <t>Домодедово, ул.Корнеева, д. 48, кв. 71</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Луганская, д. 4 к 1</t>
+          <t>Город Москва, ул.Луганская, д. 4 к 1, кв. 310</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Луганская, д. 3 к 1</t>
+          <t>Город Москва, ул.Луганская, д. 3 к 1, кв. 41</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Весёлая, д. 33 к 7</t>
+          <t>Город Москва, ул.Весёлая, д. 33 к 7, кв. 63</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Луганская, д. 1</t>
+          <t>Город Москва, ул.Луганская, д. 1, кв. 205</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Кантемировская, д. 5 к 2</t>
+          <t>Город Москва, ул.Кантемировская, д. 5 к 2, кв. 406</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Загорьевский, д. 7 к 2</t>
+          <t>Город Москва, проезд.Загорьевский, д. 7 к 2, кв. 407</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Маршала Захарова, д. 18 к 1</t>
+          <t>Город Москва, ул.Маршала Захарова, д. 18 к 1, кв. 270</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Генерала Белова, д. 45 к 2</t>
+          <t>Город Москва, ул.Генерала Белова, д. 45 к 2, кв. 243</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Шипиловская, д. 38</t>
+          <t>Город Москва, ул.Шипиловская, д. 38, кв. 188</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Гурьевский, д. 19 к 2</t>
+          <t>Город Москва, проезд.Гурьевский, д. 19 к 2, кв. 215</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Борисовский, д. 44 к 3</t>
+          <t>Город Москва, проезд.Борисовский, д. 44 к 3, кв. 455</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Ореховый, д. 23 к 1</t>
+          <t>Город Москва, проезд.Ореховый, д. 23 к 1, кв. 38</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Булатниковская, д. 4 к 1</t>
+          <t>Город Москва, ул.Булатниковская, д. 4 к 1, кв. 112</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Ореховый, д. 61 к 1</t>
+          <t>Город Москва, б-р.Ореховый, д. 61 к 1, кв. 319</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Домодедово, проезд.Кутузовский, д. 16</t>
+          <t>Домодедово, проезд.Кутузовский, д. 16, кв. 55</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Кашира, ул.Ленина, д. 11 к 3</t>
+          <t>Кашира, ул.Ленина, д. 11 к 3, кв. 87</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Кашира, ул.Металлургов, д. 5 к 3</t>
+          <t>Кашира, ул.Металлургов, д. 5 к 3, кв. 56</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Мусы Джалиля, д. 9 к 1</t>
+          <t>Город Москва, ул.Мусы Джалиля, д. 9 к 1, кв. 89</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
